--- a/frontend/public/resources/template/任务工单管理导入模板.xlsx
+++ b/frontend/public/resources/template/任务工单管理导入模板.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="任务工单管理" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,18 +27,27 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF0000"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,13 +55,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,28 +446,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>编号</t>
+          <t>项目名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>TL</t>
+          <t>所属TL</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>任务描述</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>开始日期</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>结束日期</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>预计工时</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>责任人</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>完成状态</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>实际完成日期</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>实际工时</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>实际完成人</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>任务进度跟进描述</t>
         </is>
       </c>
     </row>
